--- a/shade-schedule-template.xlsx
+++ b/shade-schedule-template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t xml:space="preserve">Schattenplaner — Schattenplan-Vorlage / Shade Schedule Template</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Abenddienst</t>
   </si>
   <si>
-    <t xml:space="preserve">18:00, 18:30, 19:00, 19:30, 20:00 — halbstündlich / half-hourly</t>
+    <t xml:space="preserve">17:00–20:00, halbstündlich / half-hourly</t>
   </si>
   <si>
     <t xml:space="preserve">Eine Zeile pro Tisch pro Monat / One row per table per month</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">Mittagdienst (11:00–15:00, stündlich)</t>
   </si>
   <si>
-    <t xml:space="preserve">Abenddienst (18:00–20:00, halbstündlich)</t>
+    <t xml:space="preserve">Abenddienst (17:00–20:00, halbstündlich)</t>
   </si>
   <si>
     <t xml:space="preserve">Month (Monat)</t>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
   </si>
   <si>
     <t xml:space="preserve">18:00</t>
@@ -716,13 +722,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="4" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -748,6 +754,8 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -767,6 +775,8 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -786,6 +796,8 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -805,6 +817,8 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -824,6 +838,8 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -843,6 +859,8 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="4" t="s">
@@ -859,6 +877,8 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
@@ -900,46 +920,54 @@
       <c r="M9" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="N9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>30</v>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
@@ -952,13 +980,15 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
@@ -971,13 +1001,15 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -990,13 +1022,15 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
@@ -1009,13 +1043,15 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
@@ -1028,13 +1064,15 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
@@ -1047,13 +1085,15 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
@@ -1066,13 +1106,15 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
@@ -1085,13 +1127,15 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1104,13 +1148,15 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="11"/>
@@ -1123,13 +1169,15 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="11"/>
@@ -1142,13 +1190,15 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
@@ -1161,13 +1211,15 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="11"/>
@@ -1180,13 +1232,15 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="11"/>
@@ -1199,13 +1253,15 @@
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
@@ -1218,13 +1274,15 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="11"/>
@@ -1237,13 +1295,15 @@
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="11"/>
@@ -1256,13 +1316,15 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -1275,13 +1337,15 @@
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="11"/>
@@ -1294,13 +1358,15 @@
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="11"/>
@@ -1313,13 +1379,15 @@
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -1332,13 +1400,15 @@
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="11"/>
@@ -1351,17 +1421,19 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B6:M6"/>
-    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="B5:O5"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="B7:O7"/>
     <mergeCell ref="D8:H8"/>
-    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="I8:O8"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1390,15 +1462,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1407,10 +1479,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1419,10 +1491,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -1431,10 +1503,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1443,10 +1515,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1455,33 +1527,33 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="n">
@@ -1491,31 +1563,31 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="n">
         <v>12</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="n">
